--- a/output/graficos_dimensiones/comunal_d_env_a_2021_o higgins.xlsx
+++ b/output/graficos_dimensiones/comunal_d_env_a_2021_o higgins.xlsx
@@ -141,7 +141,7 @@
     <t xml:space="preserve">Fecha de creación</t>
   </si>
   <si>
-    <t xml:space="preserve">2026-09-06 22:17</t>
+    <t xml:space="preserve">2026-09-10 01:31</t>
   </si>
   <si>
     <t xml:space="preserve">Fuente</t>

--- a/output/graficos_dimensiones/comunal_d_env_a_2021_o higgins.xlsx
+++ b/output/graficos_dimensiones/comunal_d_env_a_2021_o higgins.xlsx
@@ -141,7 +141,7 @@
     <t xml:space="preserve">Fecha de creación</t>
   </si>
   <si>
-    <t xml:space="preserve">2026-09-10 01:31</t>
+    <t xml:space="preserve">2026-09-12 22:42</t>
   </si>
   <si>
     <t xml:space="preserve">Fuente</t>

--- a/output/graficos_dimensiones/comunal_d_env_a_2021_o higgins.xlsx
+++ b/output/graficos_dimensiones/comunal_d_env_a_2021_o higgins.xlsx
@@ -51,21 +51,24 @@
     <t xml:space="preserve">Lolol</t>
   </si>
   <si>
+    <t xml:space="preserve">Marchigüe</t>
+  </si>
+  <si>
     <t xml:space="preserve">Peralillo</t>
   </si>
   <si>
     <t xml:space="preserve">Palmilla</t>
   </si>
   <si>
+    <t xml:space="preserve">Malloa</t>
+  </si>
+  <si>
     <t xml:space="preserve">Coinco</t>
   </si>
   <si>
     <t xml:space="preserve">Chépica</t>
   </si>
   <si>
-    <t xml:space="preserve">Malloa</t>
-  </si>
-  <si>
     <t xml:space="preserve">Pichidegua</t>
   </si>
   <si>
@@ -87,15 +90,15 @@
     <t xml:space="preserve">Santa Cruz</t>
   </si>
   <si>
+    <t xml:space="preserve">Codegua</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Nancagua</t>
+  </si>
+  <si>
     <t xml:space="preserve">Pichilemu</t>
   </si>
   <si>
-    <t xml:space="preserve">Codegua</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Nancagua</t>
-  </si>
-  <si>
     <t xml:space="preserve">Las Cabras</t>
   </si>
   <si>
@@ -132,16 +135,13 @@
     <t xml:space="preserve">Machalí</t>
   </si>
   <si>
-    <t xml:space="preserve">Marchigüe</t>
-  </si>
-  <si>
     <t xml:space="preserve">Campo</t>
   </si>
   <si>
     <t xml:space="preserve">Fecha de creación</t>
   </si>
   <si>
-    <t xml:space="preserve">2026-09-12 22:42</t>
+    <t xml:space="preserve">2026-09-24 00:11</t>
   </si>
   <si>
     <t xml:space="preserve">Fuente</t>
@@ -577,7 +577,7 @@
         <v>2021</v>
       </c>
       <c r="E2" s="2" t="n">
-        <v>195.36</v>
+        <v>208.38</v>
       </c>
     </row>
     <row r="3">
@@ -594,7 +594,7 @@
         <v>2021</v>
       </c>
       <c r="E3" s="2" t="n">
-        <v>194.92</v>
+        <v>207.16</v>
       </c>
     </row>
     <row r="4">
@@ -611,7 +611,7 @@
         <v>2021</v>
       </c>
       <c r="E4" s="2" t="n">
-        <v>169.27</v>
+        <v>180.29</v>
       </c>
     </row>
     <row r="5">
@@ -628,7 +628,7 @@
         <v>2021</v>
       </c>
       <c r="E5" s="2" t="n">
-        <v>165.42</v>
+        <v>177.58</v>
       </c>
     </row>
     <row r="6">
@@ -645,7 +645,7 @@
         <v>2021</v>
       </c>
       <c r="E6" s="2" t="n">
-        <v>159.67</v>
+        <v>170.41</v>
       </c>
     </row>
     <row r="7">
@@ -656,13 +656,13 @@
         <v>11</v>
       </c>
       <c r="C7" s="2" t="n">
-        <v>6307</v>
+        <v>6204</v>
       </c>
       <c r="D7" s="2" t="n">
         <v>2021</v>
       </c>
       <c r="E7" s="2" t="n">
-        <v>145.08</v>
+        <v>167.92</v>
       </c>
     </row>
     <row r="8">
@@ -673,13 +673,13 @@
         <v>12</v>
       </c>
       <c r="C8" s="2" t="n">
-        <v>6306</v>
+        <v>6307</v>
       </c>
       <c r="D8" s="2" t="n">
         <v>2021</v>
       </c>
       <c r="E8" s="2" t="n">
-        <v>142.81</v>
+        <v>157.09</v>
       </c>
     </row>
     <row r="9">
@@ -690,13 +690,13 @@
         <v>13</v>
       </c>
       <c r="C9" s="2" t="n">
-        <v>6103</v>
+        <v>6306</v>
       </c>
       <c r="D9" s="2" t="n">
         <v>2021</v>
       </c>
       <c r="E9" s="2" t="n">
-        <v>135.02</v>
+        <v>155.45</v>
       </c>
     </row>
     <row r="10">
@@ -707,13 +707,13 @@
         <v>14</v>
       </c>
       <c r="C10" s="2" t="n">
-        <v>6302</v>
+        <v>6109</v>
       </c>
       <c r="D10" s="2" t="n">
         <v>2021</v>
       </c>
       <c r="E10" s="2" t="n">
-        <v>134.88</v>
+        <v>145.19</v>
       </c>
     </row>
     <row r="11">
@@ -724,13 +724,13 @@
         <v>15</v>
       </c>
       <c r="C11" s="2" t="n">
-        <v>6109</v>
+        <v>6103</v>
       </c>
       <c r="D11" s="2" t="n">
         <v>2021</v>
       </c>
       <c r="E11" s="2" t="n">
-        <v>134.84</v>
+        <v>144.61</v>
       </c>
     </row>
     <row r="12">
@@ -741,13 +741,13 @@
         <v>16</v>
       </c>
       <c r="C12" s="2" t="n">
-        <v>6113</v>
+        <v>6302</v>
       </c>
       <c r="D12" s="2" t="n">
         <v>2021</v>
       </c>
       <c r="E12" s="2" t="n">
-        <v>133.76</v>
+        <v>144.44</v>
       </c>
     </row>
     <row r="13">
@@ -758,13 +758,13 @@
         <v>17</v>
       </c>
       <c r="C13" s="2" t="n">
-        <v>6203</v>
+        <v>6113</v>
       </c>
       <c r="D13" s="2" t="n">
         <v>2021</v>
       </c>
       <c r="E13" s="2" t="n">
-        <v>129.44</v>
+        <v>143.38</v>
       </c>
     </row>
     <row r="14">
@@ -775,13 +775,13 @@
         <v>18</v>
       </c>
       <c r="C14" s="2" t="n">
-        <v>6308</v>
+        <v>6203</v>
       </c>
       <c r="D14" s="2" t="n">
         <v>2021</v>
       </c>
       <c r="E14" s="2" t="n">
-        <v>129.21</v>
+        <v>138.73</v>
       </c>
     </row>
     <row r="15">
@@ -792,13 +792,13 @@
         <v>19</v>
       </c>
       <c r="C15" s="2" t="n">
-        <v>6114</v>
+        <v>6308</v>
       </c>
       <c r="D15" s="2" t="n">
         <v>2021</v>
       </c>
       <c r="E15" s="2" t="n">
-        <v>126.39</v>
+        <v>138.48</v>
       </c>
     </row>
     <row r="16">
@@ -809,13 +809,13 @@
         <v>20</v>
       </c>
       <c r="C16" s="2" t="n">
-        <v>6117</v>
+        <v>6114</v>
       </c>
       <c r="D16" s="2" t="n">
         <v>2021</v>
       </c>
       <c r="E16" s="2" t="n">
-        <v>125.92</v>
+        <v>136.47</v>
       </c>
     </row>
     <row r="17">
@@ -826,13 +826,13 @@
         <v>21</v>
       </c>
       <c r="C17" s="2" t="n">
-        <v>6112</v>
+        <v>6117</v>
       </c>
       <c r="D17" s="2" t="n">
         <v>2021</v>
       </c>
       <c r="E17" s="2" t="n">
-        <v>125.59</v>
+        <v>136.14</v>
       </c>
     </row>
     <row r="18">
@@ -843,13 +843,13 @@
         <v>22</v>
       </c>
       <c r="C18" s="2" t="n">
-        <v>6310</v>
+        <v>6112</v>
       </c>
       <c r="D18" s="2" t="n">
         <v>2021</v>
       </c>
       <c r="E18" s="2" t="n">
-        <v>119.73</v>
+        <v>134.18</v>
       </c>
     </row>
     <row r="19">
@@ -860,13 +860,13 @@
         <v>23</v>
       </c>
       <c r="C19" s="2" t="n">
-        <v>6201</v>
+        <v>6310</v>
       </c>
       <c r="D19" s="2" t="n">
         <v>2021</v>
       </c>
       <c r="E19" s="2" t="n">
-        <v>116.09</v>
+        <v>128.75</v>
       </c>
     </row>
     <row r="20">
@@ -883,7 +883,7 @@
         <v>2021</v>
       </c>
       <c r="E20" s="2" t="n">
-        <v>115.39</v>
+        <v>124.86</v>
       </c>
     </row>
     <row r="21">
@@ -900,7 +900,7 @@
         <v>2021</v>
       </c>
       <c r="E21" s="2" t="n">
-        <v>115.01</v>
+        <v>124.24</v>
       </c>
     </row>
     <row r="22">
@@ -911,13 +911,13 @@
         <v>26</v>
       </c>
       <c r="C22" s="2" t="n">
-        <v>6107</v>
+        <v>6201</v>
       </c>
       <c r="D22" s="2" t="n">
         <v>2021</v>
       </c>
       <c r="E22" s="2" t="n">
-        <v>114.4</v>
+        <v>123.53</v>
       </c>
     </row>
     <row r="23">
@@ -928,13 +928,13 @@
         <v>27</v>
       </c>
       <c r="C23" s="2" t="n">
-        <v>6104</v>
+        <v>6107</v>
       </c>
       <c r="D23" s="2" t="n">
         <v>2021</v>
       </c>
       <c r="E23" s="2" t="n">
-        <v>114.25</v>
+        <v>123.11</v>
       </c>
     </row>
     <row r="24">
@@ -945,13 +945,13 @@
         <v>28</v>
       </c>
       <c r="C24" s="2" t="n">
-        <v>6303</v>
+        <v>6104</v>
       </c>
       <c r="D24" s="2" t="n">
         <v>2021</v>
       </c>
       <c r="E24" s="2" t="n">
-        <v>110.12</v>
+        <v>122.81</v>
       </c>
     </row>
     <row r="25">
@@ -962,13 +962,13 @@
         <v>29</v>
       </c>
       <c r="C25" s="2" t="n">
-        <v>6301</v>
+        <v>6303</v>
       </c>
       <c r="D25" s="2" t="n">
         <v>2021</v>
       </c>
       <c r="E25" s="2" t="n">
-        <v>107.5</v>
+        <v>117.96</v>
       </c>
     </row>
     <row r="26">
@@ -979,13 +979,13 @@
         <v>30</v>
       </c>
       <c r="C26" s="2" t="n">
-        <v>6105</v>
+        <v>6301</v>
       </c>
       <c r="D26" s="2" t="n">
         <v>2021</v>
       </c>
       <c r="E26" s="2" t="n">
-        <v>102.95</v>
+        <v>115.27</v>
       </c>
     </row>
     <row r="27">
@@ -996,13 +996,13 @@
         <v>31</v>
       </c>
       <c r="C27" s="2" t="n">
-        <v>6101</v>
+        <v>6105</v>
       </c>
       <c r="D27" s="2" t="n">
         <v>2021</v>
       </c>
       <c r="E27" s="2" t="n">
-        <v>102.6</v>
+        <v>110.77</v>
       </c>
     </row>
     <row r="28">
@@ -1013,13 +1013,13 @@
         <v>32</v>
       </c>
       <c r="C28" s="2" t="n">
-        <v>6111</v>
+        <v>6101</v>
       </c>
       <c r="D28" s="2" t="n">
         <v>2021</v>
       </c>
       <c r="E28" s="2" t="n">
-        <v>101.21</v>
+        <v>110.36</v>
       </c>
     </row>
     <row r="29">
@@ -1030,13 +1030,13 @@
         <v>33</v>
       </c>
       <c r="C29" s="2" t="n">
-        <v>6115</v>
+        <v>6111</v>
       </c>
       <c r="D29" s="2" t="n">
         <v>2021</v>
       </c>
       <c r="E29" s="2" t="n">
-        <v>100.28</v>
+        <v>109.29</v>
       </c>
     </row>
     <row r="30">
@@ -1047,13 +1047,13 @@
         <v>34</v>
       </c>
       <c r="C30" s="2" t="n">
-        <v>6110</v>
+        <v>6115</v>
       </c>
       <c r="D30" s="2" t="n">
         <v>2021</v>
       </c>
       <c r="E30" s="2" t="n">
-        <v>99.65</v>
+        <v>107.82</v>
       </c>
     </row>
     <row r="31">
@@ -1064,13 +1064,13 @@
         <v>35</v>
       </c>
       <c r="C31" s="2" t="n">
-        <v>6116</v>
+        <v>6110</v>
       </c>
       <c r="D31" s="2" t="n">
         <v>2021</v>
       </c>
       <c r="E31" s="2" t="n">
-        <v>92.31</v>
+        <v>107.05</v>
       </c>
     </row>
     <row r="32">
@@ -1081,13 +1081,13 @@
         <v>36</v>
       </c>
       <c r="C32" s="2" t="n">
-        <v>6106</v>
+        <v>6116</v>
       </c>
       <c r="D32" s="2" t="n">
         <v>2021</v>
       </c>
       <c r="E32" s="2" t="n">
-        <v>83.64</v>
+        <v>99.33</v>
       </c>
     </row>
     <row r="33">
@@ -1098,13 +1098,13 @@
         <v>37</v>
       </c>
       <c r="C33" s="2" t="n">
-        <v>6108</v>
+        <v>6106</v>
       </c>
       <c r="D33" s="2" t="n">
         <v>2021</v>
       </c>
       <c r="E33" s="2" t="n">
-        <v>67.9</v>
+        <v>89.72</v>
       </c>
     </row>
     <row r="34">
@@ -1115,10 +1115,14 @@
         <v>38</v>
       </c>
       <c r="C34" s="2" t="n">
-        <v>6204</v>
-      </c>
-      <c r="D34" s="2"/>
-      <c r="E34" s="2"/>
+        <v>6108</v>
+      </c>
+      <c r="D34" s="2" t="n">
+        <v>2021</v>
+      </c>
+      <c r="E34" s="2" t="n">
+        <v>72.8</v>
+      </c>
     </row>
   </sheetData>
   <autoFilter ref="A1:E34"/>

--- a/output/graficos_dimensiones/comunal_d_env_a_2021_o higgins.xlsx
+++ b/output/graficos_dimensiones/comunal_d_env_a_2021_o higgins.xlsx
@@ -141,7 +141,7 @@
     <t xml:space="preserve">Fecha de creación</t>
   </si>
   <si>
-    <t xml:space="preserve">2026-09-24 00:11</t>
+    <t xml:space="preserve">2026-10-02 16:26</t>
   </si>
   <si>
     <t xml:space="preserve">Fuente</t>

--- a/output/graficos_dimensiones/comunal_d_env_a_2021_o higgins.xlsx
+++ b/output/graficos_dimensiones/comunal_d_env_a_2021_o higgins.xlsx
@@ -141,7 +141,7 @@
     <t xml:space="preserve">Fecha de creación</t>
   </si>
   <si>
-    <t xml:space="preserve">2026-10-02 16:26</t>
+    <t xml:space="preserve">2026-10-04 10:42</t>
   </si>
   <si>
     <t xml:space="preserve">Fuente</t>

--- a/output/graficos_dimensiones/comunal_d_env_a_2021_o higgins.xlsx
+++ b/output/graficos_dimensiones/comunal_d_env_a_2021_o higgins.xlsx
@@ -141,7 +141,7 @@
     <t xml:space="preserve">Fecha de creación</t>
   </si>
   <si>
-    <t xml:space="preserve">2026-10-04 10:42</t>
+    <t xml:space="preserve">2026-10-05 16:33</t>
   </si>
   <si>
     <t xml:space="preserve">Fuente</t>
